--- a/DataTables/DetailText/剧情/000_04好消息.xlsx
+++ b/DataTables/DetailText/剧情/000_04好消息.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DB6CAC-0FCC-4BE4-9E44-57979F82E3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F1EC26-F968-475D-8CC4-4D17D75F3970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="6150" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -210,6 +210,10 @@
   </si>
   <si>
     <t>000_03</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -357,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -443,6 +447,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1008,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1022,7 +1032,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1047,8 +1057,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1069,8 +1082,9 @@
       <c r="H2" s="27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1085,8 +1099,9 @@
       <c r="H3" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="28"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1107,8 +1122,9 @@
       <c r="H4" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="33">
+      <c r="I4" s="28"/>
+    </row>
+    <row r="5" spans="1:9" ht="33">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1127,8 +1143,9 @@
       <c r="H5" s="27" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="28"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1149,8 +1166,9 @@
       <c r="H6" s="27" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1159,8 +1177,9 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="31"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1169,8 +1188,9 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="31"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1179,6 +1199,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
+      <c r="I9" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
